--- a/Dependencies/Takasugi_2024/PTM_heatmap_data.xlsx
+++ b/Dependencies/Takasugi_2024/PTM_heatmap_data.xlsx
@@ -468,673 +468,673 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Oxidation or Hydroxylation</t>
+          <t>Methylation</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.373638591772106</v>
+        <v>0.07837981092830108</v>
       </c>
       <c r="C2" t="n">
-        <v>2.692132316197582</v>
+        <v>0.1264987260929571</v>
       </c>
       <c r="D2" t="n">
-        <v>14.64878626164505</v>
+        <v>0.2011103339968693</v>
       </c>
       <c r="E2" t="n">
-        <v>5.837557881800426</v>
+        <v>0.05927115597873887</v>
       </c>
       <c r="F2" t="n">
-        <v>2.176429421299572</v>
+        <v>0.1227688661962113</v>
       </c>
       <c r="G2" t="n">
-        <v>15.27471464945278</v>
+        <v>0.6760065945133098</v>
       </c>
       <c r="H2" t="n">
-        <v>3.75437726610679</v>
+        <v>0.08756248513181253</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Dihydroxy</t>
+          <t>Deamidation followed by a methylation</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.100813699568036</v>
+        <v>0.02253419564188656</v>
       </c>
       <c r="C3" t="n">
-        <v>1.320149120157057</v>
+        <v>0.04946424545942553</v>
       </c>
       <c r="D3" t="n">
-        <v>1.63387855473812</v>
+        <v>0.04611447148972801</v>
       </c>
       <c r="E3" t="n">
-        <v>2.805233764709587</v>
+        <v>0.005735918320523116</v>
       </c>
       <c r="F3" t="n">
-        <v>1.050231649196041</v>
+        <v>0.04568143858463676</v>
       </c>
       <c r="G3" t="n">
-        <v>2.815520123026488</v>
+        <v>0.09657237064475853</v>
       </c>
       <c r="H3" t="n">
-        <v>1.894232855062134</v>
+        <v>0.03564490545188829</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Cysteine oxidation to cysteic acid</t>
+          <t>Ethylation</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.718802087549509</v>
+        <v>0.04506839128377312</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2948063065872201</v>
+        <v>0.02675934590427938</v>
       </c>
       <c r="D4" t="n">
-        <v>1.539493688968705</v>
+        <v>0.103757560851888</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6249755496206733</v>
+        <v>0.01338380941455394</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09210892402533091</v>
+        <v>0.0409229553987371</v>
       </c>
       <c r="G4" t="n">
-        <v>1.121143335988471</v>
+        <v>0.2805197433014415</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0526821407542843</v>
+        <v>0.05501713667574062</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Deamidation</t>
+          <t>Carboxylation</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7041724656862219</v>
+        <v>0.04114940073735807</v>
       </c>
       <c r="C5" t="n">
-        <v>1.009954572291933</v>
+        <v>0.00405444634913324</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7984449455628908</v>
+        <v>0.008966702789669333</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3434980120052555</v>
+        <v>0.01529578218806164</v>
       </c>
       <c r="F5" t="n">
-        <v>1.201214318474676</v>
+        <v>0.006661876460259528</v>
       </c>
       <c r="G5" t="n">
-        <v>1.765743200622499</v>
+        <v>0.05288486963879634</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4865350646130962</v>
+        <v>0.01317311723221958</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Formylation</t>
+          <t>Di-Methylation</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3413578434767004</v>
+        <v>0.03625066255433925</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4478788119305845</v>
+        <v>0.02270489955514615</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6186035121373835</v>
+        <v>0.07429553740011734</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1450324939577746</v>
+        <v>0.008603877480784675</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5830399933149811</v>
+        <v>0.03711616885001737</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6837362849868087</v>
+        <v>0.1678519775492232</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1867117047320958</v>
+        <v>0.0457184656882915</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2-amino-3-oxo-butanoic_acid</t>
+          <t>Oxidation or Hydroxylation</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2994195941352772</v>
+        <v>6.324270994277295</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06398268741865493</v>
+        <v>2.74567106763303</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1033131638827383</v>
+        <v>14.78609290016473</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06106631324537876</v>
+        <v>5.863064509961379</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05317628603524259</v>
+        <v>2.060423219494554</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6077655866549411</v>
+        <v>15.56194772675538</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06430320121478819</v>
+        <v>3.683823489527759</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Amidation</t>
+          <t>Iodoacetamide derivative</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1453209105086525</v>
+        <v>0.00293924290981129</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1911381548202856</v>
+        <v>0.01135244977757307</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1109659908370152</v>
+        <v>0.011528617872432</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02767067318931225</v>
+        <v>0.009559863867538527</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1054029955341415</v>
+        <v>0.01617884283205885</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2394228068640677</v>
+        <v>0.01149671079104268</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0526821407542843</v>
+        <v>0.003874446244770466</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Dehydration</t>
+          <t>Deamidation</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1453209105086525</v>
+        <v>0.7269727463599925</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1312050045800265</v>
+        <v>1.01604425509279</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4387620787118762</v>
+        <v>0.803160378446096</v>
       </c>
       <c r="E9" t="n">
-        <v>0.154574105402365</v>
+        <v>0.3269473442698176</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1471843631332607</v>
+        <v>1.195330976297995</v>
       </c>
       <c r="G9" t="n">
-        <v>1.314523295378679</v>
+        <v>1.738302671605654</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1239579782453748</v>
+        <v>0.4796564451025837</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Reduction</t>
+          <t>Conversion of carboxylic acid to hydroxamic acid</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1306912886453653</v>
+        <v>0.01567596218566022</v>
       </c>
       <c r="C10" t="n">
-        <v>0.07451148408248422</v>
+        <v>0.07135825574474502</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01658112506759997</v>
+        <v>0.023057235744864</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007633289155672345</v>
+        <v>0.004779931933769264</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1196466435792958</v>
+        <v>0.03330938230129764</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04604284747385917</v>
+        <v>0.0873750020119244</v>
       </c>
       <c r="H10" t="n">
-        <v>0.03563791874554526</v>
+        <v>0.008523781738495025</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Loss of ammonia</t>
+          <t>Cysteine oxidation to cysteic acid</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1033826611672293</v>
+        <v>0.7171752699939549</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1303950971443474</v>
+        <v>0.278945908820367</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2461659336959073</v>
+        <v>1.543553837364507</v>
       </c>
       <c r="E11" t="n">
-        <v>0.07251624697888728</v>
+        <v>0.6280830560972812</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2241000625770937</v>
+        <v>0.09326627044363339</v>
       </c>
       <c r="G11" t="n">
-        <v>0.333810644185479</v>
+        <v>1.046200681984884</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0844463726796616</v>
+        <v>0.05036780118201606</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Methylation</t>
+          <t>Replacement of 3 protons by iron</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08290119055862723</v>
+        <v>0.005878485819622581</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1320149120157057</v>
+        <v>0.2392123345988612</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2002489719702458</v>
+        <v>0.049957344113872</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05724966866754259</v>
+        <v>0.008603877480784675</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1073021486068288</v>
+        <v>0.2265037996488239</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6422977222603354</v>
+        <v>0.01379605294925122</v>
       </c>
       <c r="H12" t="n">
-        <v>0.09064427159193035</v>
+        <v>0.006974003240586839</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Ethylation</t>
+          <t>Acetaldehyde +28</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04388886558986148</v>
+        <v>0.02743293382490538</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02996657512012952</v>
+        <v>0.01702867466635961</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1045886350417844</v>
+        <v>0.07045266477597334</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01908322288918086</v>
+        <v>0.007647891094030822</v>
       </c>
       <c r="F13" t="n">
-        <v>0.04083179106277555</v>
+        <v>0.03330938230129764</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2578399458536114</v>
+        <v>0.1609539510745976</v>
       </c>
       <c r="H13" t="n">
-        <v>0.04880845393411634</v>
+        <v>0.03641979470084238</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Carboxylation</t>
+          <t>Formylation</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04193824934142319</v>
+        <v>0.3703446066362227</v>
       </c>
       <c r="C14" t="n">
-        <v>0.003239629742716705</v>
+        <v>0.4451782091348298</v>
       </c>
       <c r="D14" t="n">
-        <v>0.008928298113323062</v>
+        <v>0.6251072801940907</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01717490060026278</v>
+        <v>0.1443539443998318</v>
       </c>
       <c r="F14" t="n">
-        <v>0.006647035754405324</v>
+        <v>0.5995688814233574</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05294927459493805</v>
+        <v>0.6461151464565988</v>
       </c>
       <c r="H14" t="n">
-        <v>0.01317053518857107</v>
+        <v>0.1836487520021201</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Di-Methylation</t>
+          <t>2-amino-3-oxo-butanoic_acid</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.03511109247188918</v>
+        <v>0.3047015149837705</v>
       </c>
       <c r="C15" t="n">
-        <v>0.02429722307037529</v>
+        <v>0.06324936304647855</v>
       </c>
       <c r="D15" t="n">
-        <v>0.07525279838372294</v>
+        <v>0.1088813910174133</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0133582560224266</v>
+        <v>0.06309510152575427</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03703348491740108</v>
+        <v>0.05519840495643608</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1565456814111212</v>
+        <v>0.6001283032924281</v>
       </c>
       <c r="H15" t="n">
-        <v>0.03873686820167963</v>
+        <v>0.06276602916528155</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Acetaldehyde +28</t>
+          <t>Amidation</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02730862747813603</v>
+        <v>0.1665570982226398</v>
       </c>
       <c r="C16" t="n">
-        <v>0.01862787102062105</v>
+        <v>0.2067767638057953</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0714263849065845</v>
+        <v>0.1165671362657013</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01240409487796756</v>
+        <v>0.02294367328209247</v>
       </c>
       <c r="F16" t="n">
-        <v>0.03323517877202662</v>
+        <v>0.1065900233641525</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1496392542900423</v>
+        <v>0.2299342158208537</v>
       </c>
       <c r="H16" t="n">
-        <v>0.03641265610957885</v>
+        <v>0.05114269043097015</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Deamidation followed by a methylation</t>
+          <t>Dehydration</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.0243827031054786</v>
+        <v>0.1440229025807532</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05183407588346728</v>
+        <v>0.131364061711917</v>
       </c>
       <c r="D17" t="n">
-        <v>0.04591696172566146</v>
+        <v>0.438087479152416</v>
       </c>
       <c r="E17" t="n">
-        <v>0.005724966866754258</v>
+        <v>0.1520018354938626</v>
       </c>
       <c r="F17" t="n">
-        <v>0.03703348491740108</v>
+        <v>0.1475129787628895</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0943878373214113</v>
+        <v>1.292230292913198</v>
       </c>
       <c r="H17" t="n">
-        <v>0.03486318138151167</v>
+        <v>0.1239822798326549</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Conversion of carboxylic acid to hydroxamic acid</t>
+          <t>Loss of ammonia</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0156049299875063</v>
+        <v>0.1028735018433952</v>
       </c>
       <c r="C18" t="n">
-        <v>0.07532139151816339</v>
+        <v>0.1192007226645173</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02295848086283073</v>
+        <v>0.253629593193504</v>
       </c>
       <c r="E18" t="n">
-        <v>0.004770805722295215</v>
+        <v>0.06405108791250813</v>
       </c>
       <c r="F18" t="n">
-        <v>0.03133602569933938</v>
+        <v>0.2226970131001042</v>
       </c>
       <c r="G18" t="n">
-        <v>0.07827284070556059</v>
+        <v>0.3265065864656122</v>
       </c>
       <c r="H18" t="n">
-        <v>0.007747373640335926</v>
+        <v>0.08136337114017979</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Prompt loss of side chain from oxidised Met</t>
+          <t>Succinic anhydride labeling reagent light form (N-term &amp; K)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.01365431373906802</v>
+        <v>0.005878485819622581</v>
       </c>
       <c r="C19" t="n">
-        <v>0.005669352049754234</v>
+        <v>0.005676224888786537</v>
       </c>
       <c r="D19" t="n">
-        <v>0.01785659622664612</v>
+        <v>0.005123830165525333</v>
       </c>
       <c r="E19" t="n">
-        <v>0.003816644577836172</v>
+        <v>0.004779931933769264</v>
       </c>
       <c r="F19" t="n">
-        <v>0.01709237765418512</v>
+        <v>0.01522714619487892</v>
       </c>
       <c r="G19" t="n">
-        <v>0.06445998646340285</v>
+        <v>0.04598684316417073</v>
       </c>
       <c r="H19" t="n">
-        <v>0.009296848368403112</v>
+        <v>0.01239822798326549</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Replacement of proton with ammonium ion</t>
+          <t>Quinone</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.01170369749062973</v>
+        <v>0.0107772240026414</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1878985250775689</v>
+        <v>0.01135244977757307</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0714263849065845</v>
+        <v>0.026900108369008</v>
       </c>
       <c r="E20" t="n">
-        <v>0.01240409487796756</v>
+        <v>0.003823945547015411</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06647035754405324</v>
+        <v>0.01332375292051906</v>
       </c>
       <c r="G20" t="n">
-        <v>0.006906427121078876</v>
+        <v>0.07127960690446464</v>
       </c>
       <c r="H20" t="n">
-        <v>0.01472000991663826</v>
+        <v>0.004649335493724559</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Quinone</t>
+          <t>Reduction</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.01072838936641058</v>
+        <v>0.1361849214879231</v>
       </c>
       <c r="C21" t="n">
-        <v>0.01052879666382929</v>
+        <v>0.07541270209387828</v>
       </c>
       <c r="D21" t="n">
-        <v>0.02550942318092303</v>
+        <v>0.02049532066210133</v>
       </c>
       <c r="E21" t="n">
-        <v>0.003816644577836172</v>
+        <v>0.01147183664104623</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01329407150881065</v>
+        <v>0.1237205628333912</v>
       </c>
       <c r="G21" t="n">
-        <v>0.07136641358448172</v>
+        <v>0.05288486963879634</v>
       </c>
       <c r="H21" t="n">
-        <v>0.004648424184201556</v>
+        <v>0.03641979470084238</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Oxidation to nitro</t>
+          <t>Replacement of proton with ammonium ion</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.008777773117972296</v>
+        <v>0.007837981092830109</v>
       </c>
       <c r="C22" t="n">
-        <v>0.004049537178395881</v>
+        <v>0.1897480891394357</v>
       </c>
       <c r="D22" t="n">
-        <v>0.02168300970378458</v>
+        <v>0.073014579858736</v>
       </c>
       <c r="E22" t="n">
-        <v>0.002862483433377129</v>
+        <v>0.01242782302780008</v>
       </c>
       <c r="F22" t="n">
-        <v>0.008546188827092559</v>
+        <v>0.06852215787695515</v>
       </c>
       <c r="G22" t="n">
-        <v>0.02532356611062255</v>
+        <v>0.006898026474625609</v>
       </c>
       <c r="H22" t="n">
-        <v>0.01239579782453748</v>
+        <v>0.01472289573012777</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Acetylation</t>
+          <t>Prompt loss of side chain from oxidised Met</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.007802464993753151</v>
+        <v>0.01371646691245269</v>
       </c>
       <c r="C23" t="n">
-        <v>0.004049537178395881</v>
+        <v>0.005676224888786537</v>
       </c>
       <c r="D23" t="n">
-        <v>0.006377355795230757</v>
+        <v>0.01793340557933867</v>
       </c>
       <c r="E23" t="n">
-        <v>0.002862483433377129</v>
+        <v>0.003823945547015411</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01709237765418512</v>
+        <v>0.01713053946923879</v>
       </c>
       <c r="G23" t="n">
-        <v>0.004604284747385917</v>
+        <v>0.06438158042983903</v>
       </c>
       <c r="H23" t="n">
-        <v>0.004648424184201556</v>
+        <v>0.009298670987449117</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Replacement of 3 protons by iron</t>
+          <t>Dihydroxy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.006827156869534008</v>
+        <v>2.125072623793563</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2502613976248654</v>
+        <v>1.310397060039863</v>
       </c>
       <c r="D24" t="n">
-        <v>0.04974337520279992</v>
+        <v>1.667806718878496</v>
       </c>
       <c r="E24" t="n">
-        <v>0.009541611444590431</v>
+        <v>2.702573515353142</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2184026033590321</v>
+        <v>1.022122188331247</v>
       </c>
       <c r="G24" t="n">
-        <v>0.01151071186846479</v>
+        <v>2.715523088844282</v>
       </c>
       <c r="H24" t="n">
-        <v>0.006972636276302334</v>
+        <v>1.887630210452171</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Iodoacetamide derivative</t>
+          <t>Oxidation to nitro</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.002925924372657432</v>
+        <v>0.008817728729433873</v>
       </c>
       <c r="C25" t="n">
-        <v>0.01214861153518764</v>
+        <v>0.00405444634913324</v>
       </c>
       <c r="D25" t="n">
-        <v>0.01147924043141537</v>
+        <v>0.02177627820348266</v>
       </c>
       <c r="E25" t="n">
-        <v>0.006679128011213302</v>
+        <v>0.002867959160261558</v>
       </c>
       <c r="F25" t="n">
-        <v>0.01329407150881065</v>
+        <v>0.008565269734619393</v>
       </c>
       <c r="G25" t="n">
-        <v>0.01151071186846479</v>
+        <v>0.02299342158208537</v>
       </c>
       <c r="H25" t="n">
-        <v>0.003873686820167963</v>
+        <v>0.01239822798326549</v>
       </c>
     </row>
   </sheetData>

--- a/Dependencies/Takasugi_2024/PTM_heatmap_data.xlsx
+++ b/Dependencies/Takasugi_2024/PTM_heatmap_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,10 +456,15 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Lung</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Muscle</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Skin</t>
         </is>
@@ -468,673 +473,1241 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Methylation</t>
+          <t>Oxidation or Hydroxylation</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.07837981092830108</v>
+        <v>4.657720264414292</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1264987260929571</v>
+        <v>3.854967588755885</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2011103339968693</v>
+        <v>6.089672151726859</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05927115597873887</v>
+        <v>4.544759282627815</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1227688661962113</v>
+        <v>4.524365813153398</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6760065945133098</v>
+        <v>4.554272384574486</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08756248513181253</v>
+        <v>10.93107262012338</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.683823489527759</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Deamidation followed by a methylation</t>
+          <t>Dihydroxy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02253419564188656</v>
+        <v>2.386665242766768</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04946424545942553</v>
+        <v>1.975326261297715</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04611447148972801</v>
+        <v>3.120412570804928</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005735918320523116</v>
+        <v>2.328782838132385</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04568143858463676</v>
+        <v>2.318333008170316</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09657237064475853</v>
+        <v>2.333657452423948</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03564490545188829</v>
+        <v>5.601197497395995</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.887630210452171</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Ethylation</t>
+          <t>Deamidation</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04506839128377312</v>
+        <v>0.6064637870577296</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02675934590427938</v>
+        <v>0.5019404580226952</v>
       </c>
       <c r="D4" t="n">
-        <v>0.103757560851888</v>
+        <v>0.7929127181150454</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01338380941455394</v>
+        <v>0.5917555734006349</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0409229553987371</v>
+        <v>0.5891002184143782</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2805197433014415</v>
+        <v>0.5929942377054285</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05501713667574062</v>
+        <v>1.423292795931084</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.4796564451025837</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Carboxylation</t>
+          <t>Formylation</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04114940073735807</v>
+        <v>0.232200189875092</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00405444634913324</v>
+        <v>0.1921807569489156</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008966702789669333</v>
+        <v>0.303586937307376</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01529578218806164</v>
+        <v>0.2265687736606631</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006661876460259528</v>
+        <v>0.225552103011644</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05288486963879634</v>
+        <v>0.2270430280067634</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01317311723221958</v>
+        <v>0.5449440914954232</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1836487520021201</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Di-Methylation</t>
+          <t>Dehydration</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03625066255433925</v>
+        <v>0.1567596218566022</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02270489955514615</v>
+        <v>0.1297422831722637</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07429553740011734</v>
+        <v>0.2049532066210133</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008603877480784675</v>
+        <v>0.1529578218806164</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03711616885001737</v>
+        <v>0.1522714619487892</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1678519775492232</v>
+        <v>0.1532779935910639</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0457184656882915</v>
+        <v>0.3678947453133659</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1239822798326549</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Oxidation or Hydroxylation</t>
+          <t>Methylation</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.324270994277295</v>
+        <v>0.1107114829362253</v>
       </c>
       <c r="C7" t="n">
-        <v>2.74567106763303</v>
+        <v>0.09163048749041122</v>
       </c>
       <c r="D7" t="n">
-        <v>14.78609290016473</v>
+        <v>0.1447482021760907</v>
       </c>
       <c r="E7" t="n">
-        <v>5.863064509961379</v>
+        <v>0.1080264617031853</v>
       </c>
       <c r="F7" t="n">
-        <v>2.060423219494554</v>
+        <v>0.1075417200013324</v>
       </c>
       <c r="G7" t="n">
-        <v>15.56194772675538</v>
+        <v>0.1082525829736889</v>
       </c>
       <c r="H7" t="n">
-        <v>3.683823489527759</v>
+        <v>0.2598256638775646</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.08756248513181253</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Iodoacetamide derivative</t>
+          <t>Loss of ammonia</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00293924290981129</v>
+        <v>0.1028735018433952</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01135244977757307</v>
+        <v>0.08514337333179804</v>
       </c>
       <c r="D8" t="n">
-        <v>0.011528617872432</v>
+        <v>0.13450054184504</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009559863867538527</v>
+        <v>0.1003785706091545</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01617884283205885</v>
+        <v>0.0999281469038929</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01149671079104268</v>
+        <v>0.1005886832941357</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003874446244770466</v>
+        <v>0.2414309266118963</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.08136337114017979</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Deamidation</t>
+          <t>2-amino-3-oxo-butanoic_acid</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7269727463599925</v>
+        <v>0.07935955856490486</v>
       </c>
       <c r="C9" t="n">
-        <v>1.01604425509279</v>
+        <v>0.0656820308559585</v>
       </c>
       <c r="D9" t="n">
-        <v>0.803160378446096</v>
+        <v>0.103757560851888</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3269473442698176</v>
+        <v>0.07743489732706207</v>
       </c>
       <c r="F9" t="n">
-        <v>1.195330976297995</v>
+        <v>0.07708742761157453</v>
       </c>
       <c r="G9" t="n">
-        <v>1.738302671605654</v>
+        <v>0.07759698425547611</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4796564451025837</v>
+        <v>0.1862467148148915</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.06276602916528155</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Conversion of carboxylic acid to hydroxamic acid</t>
+          <t>Ethylation</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01567596218566022</v>
+        <v>0.06956208219886721</v>
       </c>
       <c r="C10" t="n">
-        <v>0.07135825574474502</v>
+        <v>0.05757313815769201</v>
       </c>
       <c r="D10" t="n">
-        <v>0.023057235744864</v>
+        <v>0.09094798543807467</v>
       </c>
       <c r="E10" t="n">
-        <v>0.004779931933769264</v>
+        <v>0.06787503345952355</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03330938230129764</v>
+        <v>0.0675704612397752</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0873750020119244</v>
+        <v>0.06801710965603461</v>
       </c>
       <c r="H10" t="n">
-        <v>0.008523781738495025</v>
+        <v>0.1632532932328061</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.05501713667574062</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Cysteine oxidation to cysteic acid</t>
+          <t>Amidation</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7171752699939549</v>
+        <v>0.06466334401584839</v>
       </c>
       <c r="C11" t="n">
-        <v>0.278945908820367</v>
+        <v>0.05351869180855877</v>
       </c>
       <c r="D11" t="n">
-        <v>1.543553837364507</v>
+        <v>0.084543197731168</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6280830560972812</v>
+        <v>0.06309510152575427</v>
       </c>
       <c r="F11" t="n">
-        <v>0.09326627044363339</v>
+        <v>0.06281197805387555</v>
       </c>
       <c r="G11" t="n">
-        <v>1.046200681984884</v>
+        <v>0.06322717235631385</v>
       </c>
       <c r="H11" t="n">
-        <v>0.05036780118201606</v>
+        <v>0.1517565824417634</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.05114269043097015</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Replacement of 3 protons by iron</t>
+          <t>Cysteine oxidation to cysteic acid</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.005878485819622581</v>
+        <v>0.06368359637924463</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2392123345988612</v>
+        <v>0.05270780253873213</v>
       </c>
       <c r="D12" t="n">
-        <v>0.049957344113872</v>
+        <v>0.08326224018978667</v>
       </c>
       <c r="E12" t="n">
-        <v>0.008603877480784675</v>
+        <v>0.06213911513900042</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2265037996488239</v>
+        <v>0.06186028141669561</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01379605294925122</v>
+        <v>0.06226918489636971</v>
       </c>
       <c r="H12" t="n">
-        <v>0.006974003240586839</v>
+        <v>0.1494572402835549</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.05036780118201606</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Acetaldehyde +28</t>
+          <t>Di-Methylation</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02743293382490538</v>
+        <v>0.05780511055962204</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01702867466635961</v>
+        <v>0.04784246691977223</v>
       </c>
       <c r="D13" t="n">
-        <v>0.07045266477597334</v>
+        <v>0.07557649494149866</v>
       </c>
       <c r="E13" t="n">
-        <v>0.007647891094030822</v>
+        <v>0.0564031968184773</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03330938230129764</v>
+        <v>0.05615010159361601</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1609539510745976</v>
+        <v>0.05652126013670481</v>
       </c>
       <c r="H13" t="n">
-        <v>0.03641979470084238</v>
+        <v>0.1356611873343037</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.0457184656882915</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Formylation</t>
+          <t>Acetaldehyde +28</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3703446066362227</v>
+        <v>0.04604813892037689</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4451782091348298</v>
+        <v>0.03811179568185246</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6251072801940907</v>
+        <v>0.06020500444492267</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1443539443998318</v>
+        <v>0.04493136017743108</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5995688814233574</v>
+        <v>0.04472974194745683</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6461151464565988</v>
+        <v>0.04502541061737503</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1836487520021201</v>
+        <v>0.1080690814358012</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.03641979470084238</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2-amino-3-oxo-butanoic_acid</t>
+          <t>Reduction</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3047015149837705</v>
+        <v>0.04604813892037689</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06324936304647855</v>
+        <v>0.03811179568185246</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1088813910174133</v>
+        <v>0.06020500444492267</v>
       </c>
       <c r="E15" t="n">
-        <v>0.06309510152575427</v>
+        <v>0.04493136017743108</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05519840495643608</v>
+        <v>0.04472974194745683</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6001283032924281</v>
+        <v>0.04502541061737503</v>
       </c>
       <c r="H15" t="n">
-        <v>0.06276602916528155</v>
+        <v>0.1080690814358012</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.03641979470084238</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Amidation</t>
+          <t>Deamidation followed by a methylation</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1665570982226398</v>
+        <v>0.04506839128377312</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2067767638057953</v>
+        <v>0.03730090641202581</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1165671362657013</v>
+        <v>0.05892404690354133</v>
       </c>
       <c r="E16" t="n">
-        <v>0.02294367328209247</v>
+        <v>0.04397537379067722</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1065900233641525</v>
+        <v>0.0437780453102769</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2299342158208537</v>
+        <v>0.04406742315743087</v>
       </c>
       <c r="H16" t="n">
-        <v>0.05114269043097015</v>
+        <v>0.1057697392775927</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.03564490545188829</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Dehydration</t>
+          <t>Phosphorylation</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1440229025807532</v>
+        <v>0.01959495273207527</v>
       </c>
       <c r="C17" t="n">
-        <v>0.131364061711917</v>
+        <v>0.01621778539653296</v>
       </c>
       <c r="D17" t="n">
-        <v>0.438087479152416</v>
+        <v>0.02561915082762667</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1520018354938626</v>
+        <v>0.01911972773507705</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1475129787628895</v>
+        <v>0.01903393274359865</v>
       </c>
       <c r="G17" t="n">
-        <v>1.292230292913198</v>
+        <v>0.01915974919888299</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1239822798326549</v>
+        <v>0.04598684316417073</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.01549778497908186</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Loss of ammonia</t>
+          <t>Replacement of proton with ammonium ion</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1028735018433952</v>
+        <v>0.01861520509547151</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1192007226645173</v>
+        <v>0.01540689612670631</v>
       </c>
       <c r="D18" t="n">
-        <v>0.253629593193504</v>
+        <v>0.02433819328624533</v>
       </c>
       <c r="E18" t="n">
-        <v>0.06405108791250813</v>
+        <v>0.0181637413483232</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2226970131001042</v>
+        <v>0.01808223610641872</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3265065864656122</v>
+        <v>0.01820176173893884</v>
       </c>
       <c r="H18" t="n">
-        <v>0.08136337114017979</v>
+        <v>0.0436875010059622</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.01472289573012777</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Succinic anhydride labeling reagent light form (N-term &amp; K)</t>
+          <t>Carboxylation</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.005878485819622581</v>
+        <v>0.01665570982226398</v>
       </c>
       <c r="C19" t="n">
-        <v>0.005676224888786537</v>
+        <v>0.01378511758705302</v>
       </c>
       <c r="D19" t="n">
-        <v>0.005123830165525333</v>
+        <v>0.02177627820348266</v>
       </c>
       <c r="E19" t="n">
-        <v>0.004779931933769264</v>
+        <v>0.01625176857481549</v>
       </c>
       <c r="F19" t="n">
-        <v>0.01522714619487892</v>
+        <v>0.01617884283205885</v>
       </c>
       <c r="G19" t="n">
-        <v>0.04598684316417073</v>
+        <v>0.01628578681905054</v>
       </c>
       <c r="H19" t="n">
-        <v>0.01239822798326549</v>
+        <v>0.03908881668954512</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.01317311723221958</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Quinone</t>
+          <t>Oxidation to nitro</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0107772240026414</v>
+        <v>0.01567596218566022</v>
       </c>
       <c r="C20" t="n">
-        <v>0.01135244977757307</v>
+        <v>0.01297422831722637</v>
       </c>
       <c r="D20" t="n">
-        <v>0.026900108369008</v>
+        <v>0.02049532066210133</v>
       </c>
       <c r="E20" t="n">
-        <v>0.003823945547015411</v>
+        <v>0.01529578218806164</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01332375292051906</v>
+        <v>0.01522714619487892</v>
       </c>
       <c r="G20" t="n">
-        <v>0.07127960690446464</v>
+        <v>0.01532779935910639</v>
       </c>
       <c r="H20" t="n">
-        <v>0.004649335493724559</v>
+        <v>0.03678947453133659</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.01239822798326549</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Reduction</t>
+          <t>Succinic anhydride labeling reagent light form (N-term &amp; K)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1361849214879231</v>
+        <v>0.01567596218566022</v>
       </c>
       <c r="C21" t="n">
-        <v>0.07541270209387828</v>
+        <v>0.01297422831722637</v>
       </c>
       <c r="D21" t="n">
         <v>0.02049532066210133</v>
       </c>
       <c r="E21" t="n">
-        <v>0.01147183664104623</v>
+        <v>0.01529578218806164</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1237205628333912</v>
+        <v>0.01522714619487892</v>
       </c>
       <c r="G21" t="n">
-        <v>0.05288486963879634</v>
+        <v>0.01532779935910639</v>
       </c>
       <c r="H21" t="n">
-        <v>0.03641979470084238</v>
+        <v>0.03678947453133659</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.01239822798326549</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Replacement of proton with ammonium ion</t>
+          <t>Prompt loss of side chain from oxidised Met</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.007837981092830109</v>
+        <v>0.01175697163924516</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1897480891394357</v>
+        <v>0.009730671237919776</v>
       </c>
       <c r="D22" t="n">
-        <v>0.073014579858736</v>
+        <v>0.015371490496576</v>
       </c>
       <c r="E22" t="n">
-        <v>0.01242782302780008</v>
+        <v>0.01147183664104623</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06852215787695515</v>
+        <v>0.01142035964615919</v>
       </c>
       <c r="G22" t="n">
-        <v>0.006898026474625609</v>
+        <v>0.01149584951932979</v>
       </c>
       <c r="H22" t="n">
-        <v>0.01472289573012777</v>
+        <v>0.02759210589850244</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.009298670987449117</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Prompt loss of side chain from oxidised Met</t>
+          <t>Conversion of carboxylic acid to hydroxamic acid</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.01371646691245269</v>
+        <v>0.0107772240026414</v>
       </c>
       <c r="C23" t="n">
-        <v>0.005676224888786537</v>
+        <v>0.008919781968093128</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01793340557933867</v>
+        <v>0.01409053295519467</v>
       </c>
       <c r="E23" t="n">
-        <v>0.003823945547015411</v>
+        <v>0.01051585025429238</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01713053946923879</v>
+        <v>0.01046866300897926</v>
       </c>
       <c r="G23" t="n">
-        <v>0.06438158042983903</v>
+        <v>0.01053786205938564</v>
       </c>
       <c r="H23" t="n">
-        <v>0.009298670987449117</v>
+        <v>0.02529276374029391</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.008523781738495025</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Dihydroxy</t>
+          <t>Replacement of 3 protons by iron</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.125072623793563</v>
+        <v>0.008817728729433873</v>
       </c>
       <c r="C24" t="n">
-        <v>1.310397060039863</v>
+        <v>0.007298003428439833</v>
       </c>
       <c r="D24" t="n">
-        <v>1.667806718878496</v>
+        <v>0.011528617872432</v>
       </c>
       <c r="E24" t="n">
-        <v>2.702573515353142</v>
+        <v>0.008603877480784675</v>
       </c>
       <c r="F24" t="n">
-        <v>1.022122188331247</v>
+        <v>0.008565269734619393</v>
       </c>
       <c r="G24" t="n">
-        <v>2.715523088844282</v>
+        <v>0.008621887139497344</v>
       </c>
       <c r="H24" t="n">
-        <v>1.887630210452171</v>
+        <v>0.02069407942387683</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.006974003240586839</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Oxidation to nitro</t>
+          <t>N-Acetylhexosamine</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.008817728729433873</v>
+        <v>0.006858233456226345</v>
       </c>
       <c r="C25" t="n">
+        <v>0.005676224888786537</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.008966702789669333</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.006691904707276969</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.006661876460259528</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.006705912219609046</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.01609539510745976</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.005424224742678653</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Quinone</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.005878485819622581</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.004865335618959888</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.007685745248288</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.005735918320523116</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.005710179823079595</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.005747924759664896</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.01379605294925122</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.004649335493724559</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Hexose</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.005878485819622581</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.004865335618959888</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.007685745248288</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.005735918320523116</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.005710179823079595</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.005747924759664896</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.01379605294925122</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.004649335493724559</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Acetylation</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.005878485819622581</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.004865335618959888</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.007685745248288</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.005735918320523116</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.005710179823079595</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.005747924759664896</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.01379605294925122</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.004649335493724559</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Acrylamide adduct</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.004898738183018818</v>
+      </c>
+      <c r="C29" t="n">
         <v>0.00405444634913324</v>
       </c>
-      <c r="D25" t="n">
-        <v>0.02177627820348266</v>
-      </c>
-      <c r="E25" t="n">
+      <c r="D29" t="n">
+        <v>0.006404787706906666</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.004779931933769264</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.004758483185899662</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.004789937299720747</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.01149671079104268</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.003874446244770466</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>O-Sulfonation</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.004898738183018818</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.00405444634913324</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.006404787706906666</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.004779931933769264</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.004758483185899662</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.004789937299720747</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.01149671079104268</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.003874446244770466</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Iodoacetamide derivative</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.004898738183018818</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.00405444634913324</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.006404787706906666</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.004779931933769264</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.004758483185899662</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.004789937299720747</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.01149671079104268</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.003874446244770466</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Addition of Glycine</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.004898738183018818</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.00405444634913324</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.006404787706906666</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.004779931933769264</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.004758483185899662</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.004789937299720747</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.01149671079104268</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.003874446244770466</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Tri-Methylation</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.003918990546415054</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.003243557079306592</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.005123830165525333</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.003823945547015411</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.00380678654871973</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.003831949839776598</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.009197368632834147</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.003099556995816373</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Carbamylation</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.00293924290981129</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.002432667809479944</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.003842872624144</v>
+      </c>
+      <c r="E34" t="n">
         <v>0.002867959160261558</v>
       </c>
-      <c r="F25" t="n">
-        <v>0.008565269734619393</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.02299342158208537</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.01239822798326549</v>
+      <c r="F34" t="n">
+        <v>0.002855089911539798</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.002873962379832448</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.006898026474625609</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.002324667746862279</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Ubiquitinylation residue</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.00293924290981129</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.002432667809479944</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.003842872624144</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.002867959160261558</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.002855089911539798</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.002873962379832448</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.006898026474625609</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.002324667746862279</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Double Carbamidomethylation</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.00293924290981129</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.002432667809479944</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.003842872624144</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.002867959160261558</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.002855089911539798</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.002873962379832448</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.006898026474625609</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.002324667746862279</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Loss of O2; nitro photochemical decomposition</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.001959495273207527</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.001621778539653296</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.002561915082762667</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.001911972773507705</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.001903393274359865</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.001915974919888299</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.004598684316417074</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.001549778497908186</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>4-hydroxynonenal (HNE)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.001959495273207527</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.001621778539653296</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.002561915082762667</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.001911972773507705</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.001903393274359865</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.001915974919888299</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.004598684316417074</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.001549778497908186</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Ubiquitin D (FAT10) leaving after chymotrypsin digestion Cys-Ile-Gly-Gly</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.001959495273207527</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.001621778539653296</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.002561915082762667</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.001911972773507705</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.001903393274359865</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.001915974919888299</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.004598684316417074</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.001549778497908186</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Iodoacetic acid derivative</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.001959495273207527</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.001621778539653296</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.002561915082762667</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.001911972773507705</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.001903393274359865</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.001915974919888299</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.004598684316417074</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.001549778497908186</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>HexNAc2</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.001959495273207527</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.001621778539653296</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.002561915082762667</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.001911972773507705</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.001903393274359865</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.001915974919888299</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.004598684316417074</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.001549778497908186</v>
       </c>
     </row>
   </sheetData>

--- a/Dependencies/Takasugi_2024/PTM_heatmap_data.xlsx
+++ b/Dependencies/Takasugi_2024/PTM_heatmap_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,1241 +473,745 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Oxidation or Hydroxylation</t>
+          <t>Reduction</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.657720264414292</v>
+        <v>0.1026719829579281</v>
       </c>
       <c r="C2" t="n">
-        <v>3.854967588755885</v>
+        <v>0.05962161430970031</v>
       </c>
       <c r="D2" t="n">
-        <v>6.089672151726859</v>
+        <v>0.0152151565782254</v>
       </c>
       <c r="E2" t="n">
-        <v>4.544759282627815</v>
+        <v>0.00872794557253141</v>
       </c>
       <c r="F2" t="n">
-        <v>4.524365813153398</v>
+        <v>0.09755219042187571</v>
       </c>
       <c r="G2" t="n">
-        <v>4.554272384574486</v>
+        <v>0.007965969378813708</v>
       </c>
       <c r="H2" t="n">
-        <v>10.93107262012338</v>
+        <v>0.03666764447051921</v>
       </c>
       <c r="I2" t="n">
-        <v>3.683823489527759</v>
+        <v>0.02812964775097482</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Dihydroxy</t>
+          <t>Ethylation</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.386665242766768</v>
+        <v>0.03397777853283952</v>
       </c>
       <c r="C3" t="n">
-        <v>1.975326261297715</v>
+        <v>0.02115605669053882</v>
       </c>
       <c r="D3" t="n">
-        <v>3.120412570804928</v>
+        <v>0.07702673017726609</v>
       </c>
       <c r="E3" t="n">
-        <v>2.328782838132385</v>
+        <v>0.01018260316795331</v>
       </c>
       <c r="F3" t="n">
-        <v>2.318333008170316</v>
+        <v>0.03226726298569735</v>
       </c>
       <c r="G3" t="n">
-        <v>2.333657452423948</v>
+        <v>0.02244955006756591</v>
       </c>
       <c r="H3" t="n">
-        <v>5.601197497395995</v>
+        <v>0.194497940234928</v>
       </c>
       <c r="I3" t="n">
-        <v>1.887630210452171</v>
+        <v>0.0424937231982811</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Deamidation</t>
+          <t>2-amino-3-oxo-butanoic_acid</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6064637870577296</v>
+        <v>0.2297193287763716</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5019404580226952</v>
+        <v>0.05000522490490993</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7929127181150454</v>
+        <v>0.08083051932182243</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5917555734006349</v>
+        <v>0.04800370064892275</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5891002184143782</v>
+        <v>0.04352328495745224</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5929942377054285</v>
+        <v>0.05286506951394552</v>
       </c>
       <c r="H4" t="n">
-        <v>1.423292795931084</v>
+        <v>0.416098052469805</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4796564451025837</v>
+        <v>0.04847875463465872</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Formylation</t>
+          <t>Carboxylation</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.232200189875092</v>
+        <v>0.0310231890952013</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1921807569489156</v>
+        <v>0.003205463134930124</v>
       </c>
       <c r="D5" t="n">
-        <v>0.303586937307376</v>
+        <v>0.006656631002973613</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2265687736606631</v>
+        <v>0.01163726076337521</v>
       </c>
       <c r="F5" t="n">
-        <v>0.225552103011644</v>
+        <v>0.005252810253485615</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2270430280067634</v>
+        <v>0.01086268551656415</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5449440914954232</v>
+        <v>0.03666764447051921</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1836487520021201</v>
+        <v>0.01017455344184195</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Dehydration</t>
+          <t>Di-Methylation</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1567596218566022</v>
+        <v>0.02732995229815353</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1297422831722637</v>
+        <v>0.0179505935556087</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2049532066210133</v>
+        <v>0.05515494259606708</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1529578218806164</v>
+        <v>0.006545959179398557</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1522714619487892</v>
+        <v>0.02926565712656271</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1532779935910639</v>
+        <v>0.01810447586094024</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3678947453133659</v>
+        <v>0.1163799150586045</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1239822798326549</v>
+        <v>0.03531168547462796</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Methylation</t>
+          <t>Replacement of 3 protons by iron</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1107114829362253</v>
+        <v>0.004431884156457329</v>
       </c>
       <c r="C7" t="n">
-        <v>0.09163048749041122</v>
+        <v>0.1891223249608773</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1447482021760907</v>
+        <v>0.03708694415942441</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1080264617031853</v>
+        <v>0.006545959179398557</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1075417200013324</v>
+        <v>0.1785955486185109</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1082525829736889</v>
+        <v>0.00144835806887522</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2598256638775646</v>
+        <v>0.009565472470570231</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08756248513181253</v>
+        <v>0.005386528292739858</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Loss of ammonia</t>
+          <t>Replacement of proton with ammonium ion</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1028735018433952</v>
+        <v>0.005909178875276438</v>
       </c>
       <c r="C8" t="n">
-        <v>0.08514337333179804</v>
+        <v>0.1500156747147298</v>
       </c>
       <c r="D8" t="n">
-        <v>0.13450054184504</v>
+        <v>0.05420399530992798</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1003785706091545</v>
+        <v>0.009455274370242361</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0999281469038929</v>
+        <v>0.05402890546442347</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1005886832941357</v>
+        <v>0.02751880330862918</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2414309266118963</v>
+        <v>0.004782736235285115</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08136337114017979</v>
+        <v>0.01137155972911748</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2-amino-3-oxo-butanoic_acid</t>
+          <t>Deamidation</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07935955856490486</v>
+        <v>0.5480763406818897</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0656820308559585</v>
+        <v>0.8032890616134891</v>
       </c>
       <c r="D9" t="n">
-        <v>0.103757560851888</v>
+        <v>0.5962439484092079</v>
       </c>
       <c r="E9" t="n">
-        <v>0.07743489732706207</v>
+        <v>0.2487464488171452</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07708742761157453</v>
+        <v>0.9425042397682761</v>
       </c>
       <c r="G9" t="n">
-        <v>0.07759698425547611</v>
+        <v>0.322983849359174</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1862467148148915</v>
+        <v>1.205249531291849</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06276602916528155</v>
+        <v>0.3704734459117747</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Ethylation</t>
+          <t>Cysteine oxidation to cysteic acid</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.06956208219886721</v>
+        <v>0.5406898670877941</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05757313815769201</v>
+        <v>0.2205358636831925</v>
       </c>
       <c r="D10" t="n">
-        <v>0.09094798543807467</v>
+        <v>1.145891479797601</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06787503345952355</v>
+        <v>0.4778550200960947</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0675704612397752</v>
+        <v>0.07353934354879861</v>
       </c>
       <c r="G10" t="n">
-        <v>0.06801710965603461</v>
+        <v>0.1296280471643322</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1632532932328061</v>
+        <v>0.7253816623515759</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05501713667574062</v>
+        <v>0.03890270433645453</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Amidation</t>
+          <t>Dihydroxy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06466334401584839</v>
+        <v>1.602126122559324</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05351869180855877</v>
+        <v>1.036005685209416</v>
       </c>
       <c r="D11" t="n">
-        <v>0.084543197731168</v>
+        <v>1.238133366553092</v>
       </c>
       <c r="E11" t="n">
-        <v>0.06309510152575427</v>
+        <v>2.056158511128858</v>
       </c>
       <c r="F11" t="n">
-        <v>0.06281197805387555</v>
+        <v>0.8059311731776502</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06322717235631385</v>
+        <v>0.5025802498997013</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1517565824417634</v>
+        <v>1.882803831290574</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05114269043097015</v>
+        <v>1.457953657901588</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cysteine oxidation to cysteic acid</t>
+          <t>Acetaldehyde +28</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06368359637924463</v>
+        <v>0.02068212606346754</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05270780253873213</v>
+        <v>0.01346294516670652</v>
       </c>
       <c r="D12" t="n">
-        <v>0.08326224018978667</v>
+        <v>0.05230210073764981</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06213911513900042</v>
+        <v>0.005818630381687607</v>
       </c>
       <c r="F12" t="n">
-        <v>0.06186028141669561</v>
+        <v>0.02626405126742808</v>
       </c>
       <c r="G12" t="n">
-        <v>0.06226918489636971</v>
+        <v>0.01593193875762742</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1494572402835549</v>
+        <v>0.1115971788233194</v>
       </c>
       <c r="I12" t="n">
-        <v>0.05036780118201606</v>
+        <v>0.02812964775097482</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Di-Methylation</t>
+          <t>Conversion of carboxylic acid to hydroxamic acid</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05780511055962204</v>
+        <v>0.01181835775055288</v>
       </c>
       <c r="C13" t="n">
-        <v>0.04784246691977223</v>
+        <v>0.05641615117477018</v>
       </c>
       <c r="D13" t="n">
-        <v>0.07557649494149866</v>
+        <v>0.01711705115050358</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0564031968184773</v>
+        <v>0.003636643988554754</v>
       </c>
       <c r="F13" t="n">
-        <v>0.05615010159361601</v>
+        <v>0.02626405126742808</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05652126013670481</v>
+        <v>0.00217253710331283</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1356611873343037</v>
+        <v>0.06058132564694479</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0457184656882915</v>
+        <v>0.006583534580015382</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Acetaldehyde +28</t>
+          <t>Succinic anhydride labeling reagent light form (N-term &amp; K)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04604813892037689</v>
+        <v>0.004431884156457329</v>
       </c>
       <c r="C14" t="n">
-        <v>0.03811179568185246</v>
+        <v>0.004487648388902174</v>
       </c>
       <c r="D14" t="n">
-        <v>0.06020500444492267</v>
+        <v>0.00380378914455635</v>
       </c>
       <c r="E14" t="n">
-        <v>0.04493136017743108</v>
+        <v>0.003636643988554754</v>
       </c>
       <c r="F14" t="n">
-        <v>0.04472974194745683</v>
+        <v>0.01200642343653855</v>
       </c>
       <c r="G14" t="n">
-        <v>0.04502541061737503</v>
+        <v>0.008690148413251319</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1080690814358012</v>
+        <v>0.0318849082352341</v>
       </c>
       <c r="I14" t="n">
-        <v>0.03641979470084238</v>
+        <v>0.009576050298204191</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Reduction</t>
+          <t>Formylation</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.04604813892037689</v>
+        <v>0.2792087018568117</v>
       </c>
       <c r="C15" t="n">
-        <v>0.03811179568185246</v>
+        <v>0.3519598522153276</v>
       </c>
       <c r="D15" t="n">
-        <v>0.06020500444492267</v>
+        <v>0.4640622756358747</v>
       </c>
       <c r="E15" t="n">
-        <v>0.04493136017743108</v>
+        <v>0.1098266484543536</v>
       </c>
       <c r="F15" t="n">
-        <v>0.04472974194745683</v>
+        <v>0.4727529228137053</v>
       </c>
       <c r="G15" t="n">
-        <v>0.04502541061737503</v>
+        <v>0.1506292391630228</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1080690814358012</v>
+        <v>0.4479829607050391</v>
       </c>
       <c r="I15" t="n">
-        <v>0.03641979470084238</v>
+        <v>0.1418452450421496</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Deamidation followed by a methylation</t>
+          <t>Prompt loss of side chain from oxidised Met</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04506839128377312</v>
+        <v>0.01034106303173377</v>
       </c>
       <c r="C16" t="n">
-        <v>0.03730090641202581</v>
+        <v>0.004487648388902174</v>
       </c>
       <c r="D16" t="n">
-        <v>0.05892404690354133</v>
+        <v>0.01331326200594723</v>
       </c>
       <c r="E16" t="n">
-        <v>0.04397537379067722</v>
+        <v>0.002909315190843803</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0437780453102769</v>
+        <v>0.01350722636610587</v>
       </c>
       <c r="G16" t="n">
-        <v>0.04406742315743087</v>
+        <v>0.005069253241063269</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1057697392775927</v>
+        <v>0.04463887152932774</v>
       </c>
       <c r="I16" t="n">
-        <v>0.03564490545188829</v>
+        <v>0.007182037723653144</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Phosphorylation</t>
+          <t>Quinone</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.01959495273207527</v>
+        <v>0.008125120953505103</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01621778539653296</v>
+        <v>0.008975296777804348</v>
       </c>
       <c r="D17" t="n">
-        <v>0.02561915082762667</v>
+        <v>0.01996989300892084</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01911972773507705</v>
+        <v>0.002909315190843803</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01903393274359865</v>
+        <v>0.01050562050697123</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01915974919888299</v>
+        <v>0.007965969378813708</v>
       </c>
       <c r="H17" t="n">
-        <v>0.04598684316417073</v>
+        <v>0.04942160776461286</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01549778497908186</v>
+        <v>0.003591018861826572</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Replacement of proton with ammonium ion</t>
+          <t>Deamidation followed by a methylation</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.01861520509547151</v>
+        <v>0.01698888926641976</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01540689612670631</v>
+        <v>0.03910665024614751</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02433819328624533</v>
+        <v>0.03423410230100715</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0181637413483232</v>
+        <v>0.004363972786265705</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01808223610641872</v>
+        <v>0.03601927030961564</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01820176173893884</v>
+        <v>0.01013850648212654</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0436875010059622</v>
+        <v>0.0669583072939916</v>
       </c>
       <c r="I18" t="n">
-        <v>0.01472289573012777</v>
+        <v>0.02753114460733705</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Carboxylation</t>
+          <t>Dehydration</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.01665570982226398</v>
+        <v>0.1085811618332046</v>
       </c>
       <c r="C19" t="n">
-        <v>0.01378511758705302</v>
+        <v>0.103857005571736</v>
       </c>
       <c r="D19" t="n">
-        <v>0.02177627820348266</v>
+        <v>0.3252239718595679</v>
       </c>
       <c r="E19" t="n">
-        <v>0.01625176857481549</v>
+        <v>0.1156452788360412</v>
       </c>
       <c r="F19" t="n">
-        <v>0.01617884283205885</v>
+        <v>0.1163122270414672</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01628578681905054</v>
+        <v>0.224495500675659</v>
       </c>
       <c r="H19" t="n">
-        <v>0.03908881668954512</v>
+        <v>0.8959659214100782</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01317311723221958</v>
+        <v>0.09576050298204192</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Oxidation to nitro</t>
+          <t>Amidation</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.01567596218566022</v>
+        <v>0.1255700510996243</v>
       </c>
       <c r="C20" t="n">
-        <v>0.01297422831722637</v>
+        <v>0.1634786198814363</v>
       </c>
       <c r="D20" t="n">
-        <v>0.02049532066210133</v>
+        <v>0.08653620303865696</v>
       </c>
       <c r="E20" t="n">
-        <v>0.01529578218806164</v>
+        <v>0.01745589114506282</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01522714619487892</v>
+        <v>0.08404496405576985</v>
       </c>
       <c r="G20" t="n">
-        <v>0.01532779935910639</v>
+        <v>0.02317372910200351</v>
       </c>
       <c r="H20" t="n">
-        <v>0.03678947453133659</v>
+        <v>0.1594245411761705</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01239822798326549</v>
+        <v>0.03950120748009229</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Succinic anhydride labeling reagent light form (N-term &amp; K)</t>
+          <t>Loss of ammonia</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.01567596218566022</v>
+        <v>0.07755797273800326</v>
       </c>
       <c r="C21" t="n">
-        <v>0.01297422831722637</v>
+        <v>0.09424061616694565</v>
       </c>
       <c r="D21" t="n">
-        <v>0.02049532066210133</v>
+        <v>0.1882875626555393</v>
       </c>
       <c r="E21" t="n">
-        <v>0.01529578218806164</v>
+        <v>0.0487310294466337</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01522714619487892</v>
+        <v>0.1755939427593763</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01532779935910639</v>
+        <v>0.0514167114450703</v>
       </c>
       <c r="H21" t="n">
-        <v>0.03678947453133659</v>
+        <v>0.2263828484701621</v>
       </c>
       <c r="I21" t="n">
-        <v>0.01239822798326549</v>
+        <v>0.06284283008196501</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Prompt loss of side chain from oxidised Met</t>
+          <t>Methylation</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.01175697163924516</v>
+        <v>0.05909178875276438</v>
       </c>
       <c r="C22" t="n">
-        <v>0.009730671237919776</v>
+        <v>0.1000104498098199</v>
       </c>
       <c r="D22" t="n">
-        <v>0.015371490496576</v>
+        <v>0.1492987239238368</v>
       </c>
       <c r="E22" t="n">
-        <v>0.01147183664104623</v>
+        <v>0.04509438545807895</v>
       </c>
       <c r="F22" t="n">
-        <v>0.01142035964615919</v>
+        <v>0.09680178895709204</v>
       </c>
       <c r="G22" t="n">
-        <v>0.01149584951932979</v>
+        <v>0.0586585017894464</v>
       </c>
       <c r="H22" t="n">
-        <v>0.02759210589850244</v>
+        <v>0.4687081510579413</v>
       </c>
       <c r="I22" t="n">
-        <v>0.009298670987449117</v>
+        <v>0.0676308552310671</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Conversion of carboxylic acid to hydroxamic acid</t>
+          <t>Iodoacetamide derivative</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0107772240026414</v>
+        <v>0.002215942078228664</v>
       </c>
       <c r="C23" t="n">
-        <v>0.008919781968093128</v>
+        <v>0.008975296777804348</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01409053295519467</v>
+        <v>0.008558525575251788</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01051585025429238</v>
+        <v>0.007273287977109508</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01046866300897926</v>
+        <v>0.01275682490132221</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01053786205938564</v>
+        <v>0.005069253241063269</v>
       </c>
       <c r="H23" t="n">
-        <v>0.02529276374029391</v>
+        <v>0.007971227058808525</v>
       </c>
       <c r="I23" t="n">
-        <v>0.008523781738495025</v>
+        <v>0.00299251571818881</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Replacement of 3 protons by iron</t>
+          <t>Oxidation or Hydroxylation</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.008817728729433873</v>
+        <v>4.767968704988677</v>
       </c>
       <c r="C24" t="n">
-        <v>0.007298003428439833</v>
+        <v>2.17073963497468</v>
       </c>
       <c r="D24" t="n">
-        <v>0.011528617872432</v>
+        <v>10.97678452390349</v>
       </c>
       <c r="E24" t="n">
-        <v>0.008603877480784675</v>
+        <v>4.460707516361262</v>
       </c>
       <c r="F24" t="n">
-        <v>0.008565269734619393</v>
+        <v>1.624619171256622</v>
       </c>
       <c r="G24" t="n">
-        <v>0.008621887139497344</v>
+        <v>5.859332567634701</v>
       </c>
       <c r="H24" t="n">
-        <v>0.02069407942387683</v>
+        <v>10.78985294680322</v>
       </c>
       <c r="I24" t="n">
-        <v>0.006974003240586839</v>
+        <v>2.84528394485392</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>N-Acetylhexosamine</t>
+          <t>Oxidation to nitro</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.006858233456226345</v>
+        <v>0.006647826234685994</v>
       </c>
       <c r="C25" t="n">
-        <v>0.005676224888786537</v>
+        <v>0.003205463134930124</v>
       </c>
       <c r="D25" t="n">
-        <v>0.008966702789669333</v>
+        <v>0.01616610386436449</v>
       </c>
       <c r="E25" t="n">
-        <v>0.006691904707276969</v>
+        <v>0.002181986393132853</v>
       </c>
       <c r="F25" t="n">
-        <v>0.006661876460259528</v>
+        <v>0.006753613183052934</v>
       </c>
       <c r="G25" t="n">
-        <v>0.006705912219609046</v>
+        <v>0.01665611779206503</v>
       </c>
       <c r="H25" t="n">
-        <v>0.01609539510745976</v>
+        <v>0.01594245411761705</v>
       </c>
       <c r="I25" t="n">
-        <v>0.005424224742678653</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>Quinone</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>0.005878485819622581</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.004865335618959888</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.007685745248288</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.005735918320523116</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.005710179823079595</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.005747924759664896</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.01379605294925122</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.004649335493724559</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>Hexose</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>0.005878485819622581</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.004865335618959888</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.007685745248288</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.005735918320523116</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.005710179823079595</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.005747924759664896</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.01379605294925122</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.004649335493724559</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>Acetylation</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>0.005878485819622581</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.004865335618959888</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.007685745248288</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.005735918320523116</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.005710179823079595</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.005747924759664896</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.01379605294925122</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.004649335493724559</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>Acrylamide adduct</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>0.004898738183018818</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.00405444634913324</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.006404787706906666</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.004779931933769264</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.004758483185899662</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.004789937299720747</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.01149671079104268</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.003874446244770466</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>O-Sulfonation</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>0.004898738183018818</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.00405444634913324</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.006404787706906666</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.004779931933769264</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.004758483185899662</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.004789937299720747</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.01149671079104268</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.003874446244770466</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>Iodoacetamide derivative</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>0.004898738183018818</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.00405444634913324</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.006404787706906666</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.004779931933769264</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.004758483185899662</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.004789937299720747</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.01149671079104268</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.003874446244770466</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>Addition of Glycine</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>0.004898738183018818</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0.00405444634913324</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.006404787706906666</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.004779931933769264</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.004758483185899662</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.004789937299720747</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.01149671079104268</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.003874446244770466</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>Tri-Methylation</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>0.003918990546415054</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0.003243557079306592</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.005123830165525333</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.003823945547015411</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.00380678654871973</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.003831949839776598</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.009197368632834147</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.003099556995816373</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>Carbamylation</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>0.00293924290981129</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0.002432667809479944</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.003842872624144</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.002867959160261558</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.002855089911539798</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.002873962379832448</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.006898026474625609</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.002324667746862279</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>Ubiquitinylation residue</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>0.00293924290981129</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.002432667809479944</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.003842872624144</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.002867959160261558</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.002855089911539798</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.002873962379832448</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.006898026474625609</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.002324667746862279</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>Double Carbamidomethylation</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>0.00293924290981129</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0.002432667809479944</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.003842872624144</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.002867959160261558</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.002855089911539798</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.002873962379832448</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.006898026474625609</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.002324667746862279</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>Loss of O2; nitro photochemical decomposition</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>0.001959495273207527</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.001621778539653296</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.002561915082762667</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.001911972773507705</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.001903393274359865</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.001915974919888299</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.004598684316417074</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.001549778497908186</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>4-hydroxynonenal (HNE)</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0.001959495273207527</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0.001621778539653296</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.002561915082762667</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.001911972773507705</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.001903393274359865</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.001915974919888299</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.004598684316417074</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.001549778497908186</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>Ubiquitin D (FAT10) leaving after chymotrypsin digestion Cys-Ile-Gly-Gly</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0.001959495273207527</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0.001621778539653296</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.002561915082762667</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.001911972773507705</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.001903393274359865</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.001915974919888299</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.004598684316417074</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.001549778497908186</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Iodoacetic acid derivative</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>0.001959495273207527</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0.001621778539653296</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.002561915082762667</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.001911972773507705</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.001903393274359865</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.001915974919888299</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.004598684316417074</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.001549778497908186</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>HexNAc2</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>0.001959495273207527</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0.001621778539653296</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.002561915082762667</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.001911972773507705</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.001903393274359865</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.001915974919888299</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.004598684316417074</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.001549778497908186</v>
+        <v>0.009576050298204191</v>
       </c>
     </row>
   </sheetData>
